--- a/www/terminologies/CodeSystem-concept-properties.xlsx
+++ b/www/terminologies/CodeSystem-concept-properties.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00.000+00:00</t>
+    <t>2026-06-29T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>Code</t>
@@ -214,6 +214,15 @@
     <t>Propriété permettant de spécifier les codes exclusifs appartenant au RPPS</t>
   </si>
   <si>
+    <t>specialisationFiness</t>
+  </si>
+  <si>
+    <t>Specialisation FINESS</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant à FINESS</t>
+  </si>
+  <si>
     <t>ror</t>
   </si>
   <si>
@@ -251,6 +260,12 @@
   </si>
   <si>
     <t>epars</t>
+  </si>
+  <si>
+    <t>EPARS</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts utilisés par EPARS</t>
   </si>
   <si>
     <t>finess</t>
@@ -806,7 +821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -985,10 +1000,10 @@
         <v>78</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -996,13 +1011,13 @@
         <v>44</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -1010,13 +1025,13 @@
         <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1024,13 +1039,13 @@
         <v>44</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -1038,13 +1053,13 @@
         <v>44</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1052,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1066,13 +1081,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -1080,13 +1095,13 @@
         <v>44</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -1094,13 +1109,13 @@
         <v>44</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22">
@@ -1108,13 +1123,13 @@
         <v>44</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
@@ -1122,13 +1137,13 @@
         <v>44</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -1136,13 +1151,13 @@
         <v>44</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
@@ -1150,13 +1165,13 @@
         <v>44</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -1164,13 +1179,13 @@
         <v>44</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1178,13 +1193,13 @@
         <v>44</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
@@ -1192,13 +1207,13 @@
         <v>44</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
@@ -1206,13 +1221,13 @@
         <v>44</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
@@ -1220,13 +1235,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31">
@@ -1234,13 +1249,13 @@
         <v>44</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32">
@@ -1248,13 +1263,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33">
@@ -1262,13 +1277,13 @@
         <v>44</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -1276,13 +1291,13 @@
         <v>44</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
@@ -1290,13 +1305,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36">
@@ -1304,13 +1319,13 @@
         <v>44</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37">
@@ -1318,13 +1333,27 @@
         <v>44</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/CodeSystem-concept-properties.xlsx
+++ b/www/terminologies/CodeSystem-concept-properties.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00.000+00:00</t>
+    <t>2026-03-30T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>37</t>
+    <t>36</t>
   </si>
   <si>
     <t>Code</t>
@@ -214,15 +214,6 @@
     <t>Propriété permettant de spécifier les codes exclusifs appartenant au RPPS</t>
   </si>
   <si>
-    <t>specialisationFiness</t>
-  </si>
-  <si>
-    <t>Specialisation FINESS</t>
-  </si>
-  <si>
-    <t>Propriété permettant de spécifier les codes exclusifs appartenant à FINESS</t>
-  </si>
-  <si>
     <t>ror</t>
   </si>
   <si>
@@ -260,12 +251,6 @@
   </si>
   <si>
     <t>epars</t>
-  </si>
-  <si>
-    <t>EPARS</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts utilisés par EPARS</t>
   </si>
   <si>
     <t>finess</t>
@@ -821,7 +806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1000,10 +985,10 @@
         <v>78</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -1011,13 +996,13 @@
         <v>44</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -1025,13 +1010,13 @@
         <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1039,13 +1024,13 @@
         <v>44</v>
       </c>
       <c r="B16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -1053,13 +1038,13 @@
         <v>44</v>
       </c>
       <c r="B17" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1067,13 +1052,13 @@
         <v>44</v>
       </c>
       <c r="B18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1081,13 +1066,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -1095,13 +1080,13 @@
         <v>44</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -1109,13 +1094,13 @@
         <v>44</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>104</v>
       </c>
     </row>
     <row r="22">
@@ -1123,13 +1108,13 @@
         <v>44</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="23">
@@ -1137,13 +1122,13 @@
         <v>44</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -1151,13 +1136,13 @@
         <v>44</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>113</v>
       </c>
     </row>
     <row r="25">
@@ -1165,13 +1150,13 @@
         <v>44</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -1179,13 +1164,13 @@
         <v>44</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1193,13 +1178,13 @@
         <v>44</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>122</v>
       </c>
     </row>
     <row r="28">
@@ -1207,13 +1192,13 @@
         <v>44</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="29">
@@ -1221,13 +1206,13 @@
         <v>44</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="D29" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>128</v>
       </c>
     </row>
     <row r="30">
@@ -1235,13 +1220,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>131</v>
       </c>
     </row>
     <row r="31">
@@ -1249,13 +1234,13 @@
         <v>44</v>
       </c>
       <c r="B31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="D31" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="32">
@@ -1263,13 +1248,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D32" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>137</v>
       </c>
     </row>
     <row r="33">
@@ -1277,13 +1262,13 @@
         <v>44</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="D33" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -1291,13 +1276,13 @@
         <v>44</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="D34" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>143</v>
       </c>
     </row>
     <row r="35">
@@ -1305,13 +1290,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="D35" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="36">
@@ -1319,13 +1304,13 @@
         <v>44</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D36" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="37">
@@ -1333,27 +1318,13 @@
         <v>44</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="D37" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
